--- a/docentes/Medina Tolentino Elio - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -85,21 +85,12 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>CANTELLAN</t>
   </si>
   <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MAYA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -121,18 +112,9 @@
     <t>TZIZIHUA</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>LARA</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
     <t>SOLIS</t>
   </si>
   <si>
@@ -154,22 +136,10 @@
     <t>DORA LUZ</t>
   </si>
   <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
     <t>DANIELA DEL CARMEN</t>
   </si>
   <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
     <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
@@ -573,16 +543,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>22.22</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -638,7 +611,7 @@
         <v>18</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -697,16 +670,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>22.22</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +692,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -754,10 +730,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -777,10 +753,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -800,10 +776,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -823,10 +799,10 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -846,10 +822,10 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -869,10 +845,10 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -886,16 +862,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920318</v>
+        <v>20330051920320</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -909,16 +885,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920320</v>
+        <v>20330051920324</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -932,16 +908,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920323</v>
+        <v>20330051920333</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -950,98 +926,6 @@
         <v>9</v>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920380</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920324</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920327</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920333</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Mat</t>
   </si>
@@ -65,84 +65,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
   </si>
 </sst>
 </file>
@@ -543,19 +465,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>22.22</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -608,16 +530,19 @@
         <v>18</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>18</v>
       </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -670,19 +595,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>22.22</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -692,7 +617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -722,213 +647,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920321</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920322</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920325</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920396</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920329</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920335</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920320</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920324</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920333</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20221.xlsx
@@ -607,7 +607,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
